--- a/forms/trg/Formulir_TRG_oeceng.xlsx
+++ b/forms/trg/Formulir_TRG_oeceng.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Ir. Muhammad Arsyad Thaha, MT.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -957,7 +961,11 @@
           <t>D.Eng., Mukhsan Putra Hatta, ST., MT.</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -990,7 +998,11 @@
           <t>Dr. Ir. A. Ildha Dwi Puspita, ST., MT.</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1023,7 +1035,11 @@
           <t>Dr. Ir. Riswal Karama, ST., MT.</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1056,7 +1072,11 @@
           <t>Ir. Andi Subhan Mustari, ST., M.Eng.</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1089,7 +1109,11 @@
           <t>Ir. Silman Pongmanda, ST., MT.</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1124,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1161,7 +1185,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1198,7 +1222,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1235,7 +1259,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1272,7 +1296,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1309,7 +1333,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
